--- a/spider_telephone/电话号码判断2.xlsx
+++ b/spider_telephone/电话号码判断2.xlsx
@@ -432,481 +432,641 @@
       <c r="A2" t="n">
         <v>13509022281</v>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>13509022502</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>13509817757</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>13527916519</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>13527936712</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>13527942547</v>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>13527954868</v>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>13527993664</v>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>13528528636</v>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>13528573727</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>13528605899</v>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>13528680763</v>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13528681975</v>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>13528697335</v>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>13532340259</v>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>13532354251</v>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>13532445690</v>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>13532448020</v>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>13532516038</v>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>13532524813</v>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>13532535484</v>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>13532551077</v>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>13532580390</v>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>13532637003</v>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>13532671042</v>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>13532721023</v>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>13532734521</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>13532739374</v>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>13532811110</v>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>13532811552</v>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>13532823367</v>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>13532867526</v>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>13532880082</v>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>13532923878</v>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>13532960717</v>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>13532987368</v>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>13532997658</v>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>13537043824</v>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>13537070423</v>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>13537073529</v>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>13537076636</v>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>13537120039</v>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>13537279956</v>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>13537283790</v>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>13537408208</v>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>13537475612</v>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>13537485150</v>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>13538359694</v>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>13538429979</v>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>13538479625</v>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>13538480693</v>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>13538493223</v>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>13538550559</v>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>13538581083</v>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>13538634531</v>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>13538665688</v>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>13538687965</v>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>13539002592</v>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>13539002647</v>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>13539024025</v>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>13539038864</v>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>13539039426</v>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>13539047897</v>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>13539062216</v>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>13539086306</v>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>13539089464</v>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>13539093337</v>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>13543743066</v>
       </c>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>13543753670</v>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>13544654843</v>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>13544676043</v>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>13544689762</v>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>13544709181</v>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>13544710506</v>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>13544720070</v>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
         <v>13544721794</v>
       </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>13544766231</v>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>13544863168</v>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
         <v>13546911933</v>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
         <v>13546946294</v>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/spider_telephone/电话号码判断2.xlsx
+++ b/spider_telephone/电话号码判断2.xlsx
@@ -505,567 +505,707 @@
         <v>13528573727</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>13528605899</v>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>13528680763</v>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13528681975</v>
       </c>
-      <c r="B14" t="n">
-        <v>0</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>13528697335</v>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>13532340259</v>
       </c>
-      <c r="B16" t="n">
-        <v>0</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>13532354251</v>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>13532445690</v>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>13532448020</v>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>13532516038</v>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>13532524813</v>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>13532535484</v>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>13532551077</v>
       </c>
-      <c r="B23" t="n">
-        <v>1</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>13532580390</v>
       </c>
-      <c r="B24" t="n">
-        <v>1</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>13532637003</v>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>13532671042</v>
       </c>
-      <c r="B26" t="n">
-        <v>0</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>13532721023</v>
       </c>
-      <c r="B27" t="n">
-        <v>0</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>13532734521</v>
       </c>
-      <c r="B28" t="n">
-        <v>0</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>13532739374</v>
       </c>
-      <c r="B29" t="n">
-        <v>1</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>13532811110</v>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>13532811552</v>
       </c>
-      <c r="B31" t="n">
-        <v>0</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>13532823367</v>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>13532867526</v>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>13532880082</v>
       </c>
-      <c r="B34" t="n">
-        <v>0</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>13532923878</v>
       </c>
-      <c r="B35" t="n">
-        <v>1</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>13532960717</v>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>13532987368</v>
       </c>
-      <c r="B37" t="n">
-        <v>1</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>13532997658</v>
       </c>
-      <c r="B38" t="n">
-        <v>0</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>13537043824</v>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>13537070423</v>
       </c>
-      <c r="B40" t="n">
-        <v>0</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>13537073529</v>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>13537076636</v>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>13537120039</v>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>13537279956</v>
       </c>
-      <c r="B44" t="n">
-        <v>1</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>13537283790</v>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>13537408208</v>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>13537475612</v>
       </c>
-      <c r="B47" t="n">
-        <v>0</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>13537485150</v>
       </c>
-      <c r="B48" t="n">
-        <v>1</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>13538359694</v>
       </c>
-      <c r="B49" t="n">
-        <v>1</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>13538429979</v>
       </c>
-      <c r="B50" t="n">
-        <v>0</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>13538479625</v>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>13538480693</v>
       </c>
-      <c r="B52" t="n">
-        <v>1</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>13538493223</v>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>13538550559</v>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>13538581083</v>
       </c>
-      <c r="B55" t="n">
-        <v>0</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>13538634531</v>
       </c>
-      <c r="B56" t="n">
-        <v>0</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>13538665688</v>
       </c>
-      <c r="B57" t="n">
-        <v>0</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>13538687965</v>
       </c>
-      <c r="B58" t="n">
-        <v>0</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>13539002592</v>
       </c>
-      <c r="B59" t="n">
-        <v>0</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>13539002647</v>
       </c>
-      <c r="B60" t="n">
-        <v>1</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>13539024025</v>
       </c>
-      <c r="B61" t="n">
-        <v>0</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>13539038864</v>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>13539039426</v>
       </c>
-      <c r="B63" t="n">
-        <v>0</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>13539047897</v>
       </c>
-      <c r="B64" t="n">
-        <v>0</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>13539062216</v>
       </c>
-      <c r="B65" t="n">
-        <v>0</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>13539086306</v>
       </c>
-      <c r="B66" t="n">
-        <v>1</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>13539089464</v>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>13539093337</v>
       </c>
-      <c r="B68" t="n">
-        <v>0</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
         <v>13543743066</v>
       </c>
-      <c r="B69" t="n">
-        <v>1</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>13543753670</v>
       </c>
-      <c r="B70" t="n">
-        <v>0</v>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
         <v>13544654843</v>
       </c>
-      <c r="B71" t="n">
-        <v>0</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
         <v>13544676043</v>
       </c>
-      <c r="B72" t="n">
-        <v>0</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
         <v>13544689762</v>
       </c>
-      <c r="B73" t="n">
-        <v>1</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
         <v>13544709181</v>
       </c>
-      <c r="B74" t="n">
-        <v>0</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
         <v>13544710506</v>
       </c>
-      <c r="B75" t="n">
-        <v>0</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>13544720070</v>
       </c>
-      <c r="B76" t="n">
-        <v>0</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
         <v>13544721794</v>
       </c>
-      <c r="B77" t="n">
-        <v>0</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
         <v>13544766231</v>
       </c>
-      <c r="B78" t="n">
-        <v>0</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
         <v>13544863168</v>
       </c>
-      <c r="B79" t="n">
-        <v>1</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
         <v>13546911933</v>
       </c>
-      <c r="B80" t="n">
-        <v>1</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
         <v>13546946294</v>
       </c>
-      <c r="B81" t="n">
-        <v>0</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/spider_telephone/电话号码判断2.xlsx
+++ b/spider_telephone/电话号码判断2.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,16 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>电话号码</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>结果</t>
         </is>
@@ -430,783 +442,867 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13509022281</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
+        <v>13539086306</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>13509022502</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+        <v>13539089464</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>13509817757</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
+        <v>13539093337</v>
+      </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13527916519</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
+        <v>13543743066</v>
+      </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>13527936712</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+        <v>13543753670</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13527942547</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+        <v>13544654843</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>13527954868</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
+        <v>13544676043</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13527993664</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+        <v>13544689762</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>13528528636</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
+        <v>13544709181</v>
+      </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>13528573727</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
+        <v>13544710506</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13528605899</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13544720070</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13528680763</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13544721794</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13528681975</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13544766231</v>
+      </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13528697335</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13544863168</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13532340259</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13546911933</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>13532354251</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13546946294</v>
+      </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13532445690</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13546962609</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13532448020</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13546996722</v>
+      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13532516038</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13549213072</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>13532524813</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13549282116</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>13532535484</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13549292803</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>13532551077</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13549376864</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>13532580390</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13553828700</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>13532637003</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13553867048</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>13532671042</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13556604212</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>13532721023</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13556656667</v>
+      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13532734521</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13556685837</v>
+      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>13532739374</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13556698476</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>13532811110</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13556729591</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13532811552</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13556785927</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13532823367</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13559751560</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>13532867526</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13559782669</v>
+      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>13532880082</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13559794591</v>
+      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13532923878</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13560801360</v>
+      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>13532960717</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13560828081</v>
+      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>13532987368</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13560863234</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>13532997658</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13560878619</v>
+      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13537043824</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13580753744</v>
+      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>13537070423</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13580797529</v>
+      </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>13537073529</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13580816168</v>
+      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>13537076636</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13580828044</v>
+      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>13537120039</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13580829686</v>
+      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>13537279956</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13580859588</v>
+      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>13537283790</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13580868178</v>
+      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>13537408208</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13580880920</v>
+      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>13537475612</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13580911586</v>
+      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>13537485150</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13580956429</v>
+      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>13538359694</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13580967518</v>
+      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>13538429979</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13592714548</v>
+      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>13538479625</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13592751620</v>
+      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>13538480693</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13592770869</v>
+      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>13538493223</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13600242465</v>
+      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>13538550559</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13600256222</v>
+      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>13538581083</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13600271603</v>
+      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>13538634531</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13602333496</v>
+      </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>13538665688</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13602363442</v>
+      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>13538687965</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13602364926</v>
+      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>13539002592</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13602368245</v>
+      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>13539002647</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13602373651</v>
+      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>13539024025</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13602377728</v>
+      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>13539038864</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13602382083</v>
+      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>13539039426</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13602396639</v>
+      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>13539047897</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13602396803</v>
+      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>13539062216</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13609661189</v>
+      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>13539086306</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13612699272</v>
+      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>13539089464</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13612759585</v>
+      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>13539093337</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13620055268</v>
+      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>13543743066</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13622680860</v>
+      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>13543753670</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13622682273</v>
+      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>13544654843</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13622696269</v>
+      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>13544676043</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13631793071</v>
+      </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>13544689762</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13642380866</v>
+      </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>13544709181</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13642800825</v>
+      </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>13544710506</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13642820787</v>
+      </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>13544720070</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13642907152</v>
+      </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>13544721794</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13642912597</v>
+      </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>13544766231</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13642918499</v>
+      </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>13544863168</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13642952310</v>
+      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>13546911933</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13649802461</v>
+      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>13546946294</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>查询失败</t>
-        </is>
-      </c>
+        <v>13649820818</v>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>13650004673</v>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>13650011102</v>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>13650034071</v>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>13650035066</v>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>13650082478</v>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>13650094520</v>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>13650155157</v>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>13650218460</v>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>13650241680</v>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>13650260987</v>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>13650373337</v>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>13650381441</v>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>13650382662</v>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>13650399497</v>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>13650429899</v>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>13650448911</v>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>13652488338</v>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>13652490789</v>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>13652510966</v>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>13652521899</v>
+      </c>
+      <c r="B101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>13652525818</v>
+      </c>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>13652530798</v>
+      </c>
+      <c r="B103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>13652537477</v>
+      </c>
+      <c r="B104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>13652573083</v>
+      </c>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>13662732748</v>
+      </c>
+      <c r="B106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>13662773663</v>
+      </c>
+      <c r="B107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>13662780007</v>
+      </c>
+      <c r="B108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>13662789728</v>
+      </c>
+      <c r="B109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>13662801795</v>
+      </c>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>13662831504</v>
+      </c>
+      <c r="B111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>13662883917</v>
+      </c>
+      <c r="B112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>13662892550</v>
+      </c>
+      <c r="B113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>13662924782</v>
+      </c>
+      <c r="B114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>13662927220</v>
+      </c>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>13662978731</v>
+      </c>
+      <c r="B116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>13662999728</v>
+      </c>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>13669803831</v>
+      </c>
+      <c r="B118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>13669877757</v>
+      </c>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>13669882415</v>
+      </c>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>13669888939</v>
+      </c>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>13669888944</v>
+      </c>
+      <c r="B122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>13669895661</v>
+      </c>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>13669899465</v>
+      </c>
+      <c r="B124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>13686049100</v>
+      </c>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>13686053379</v>
+      </c>
+      <c r="B126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>13686093776</v>
+      </c>
+      <c r="B127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>13686098107</v>
+      </c>
+      <c r="B128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>13686110392</v>
+      </c>
+      <c r="B129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>13686144095</v>
+      </c>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>13686213715</v>
+      </c>
+      <c r="B131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>13686216306</v>
+      </c>
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>13686601052</v>
+      </c>
+      <c r="B133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>13686601655</v>
+      </c>
+      <c r="B134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>13686695138</v>
+      </c>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>13694912028</v>
+      </c>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>13694941815</v>
+      </c>
+      <c r="B137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>13694997368</v>
+      </c>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>13711812362</v>
+      </c>
+      <c r="B139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>13711873141</v>
+      </c>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>13711877045</v>
+      </c>
+      <c r="B141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>13711879718</v>
+      </c>
+      <c r="B142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>13711894720</v>
+      </c>
+      <c r="B143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>13711896171</v>
+      </c>
+      <c r="B144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>13711930666</v>
+      </c>
+      <c r="B145" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
